--- a/frontend-prototype/Assets/Download template.xlsx
+++ b/frontend-prototype/Assets/Download template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corpdir-my.sharepoint.com/personal/jinyozh_apac_corpdir_net/Documents/Project Documents/Transformation fields mapping/frontend-prototype/Assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_BA0B8719A0734A1BA52C859518E5B4C3270BEC2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B61633DE-5095-48EA-A517-1154B0B3CCEB}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_BA0B8719A0734A1BA52C859518E5B4C3270BEC2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{206A4E5B-B91C-4354-9238-4B7F15F5E1A3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="341">
   <si>
     <t>Transformation</t>
   </si>
@@ -1054,6 +1054,9 @@
   </si>
   <si>
     <t>Length</t>
+  </si>
+  <si>
+    <t>Group</t>
   </si>
 </sst>
 </file>
@@ -1654,7 +1657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="17.649999999999999" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.6640625" style="3" customWidth="1"/>
@@ -1674,10 +1677,11 @@
     <col min="15" max="15" width="9.5" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="6.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="16354" width="8.9140625" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" style="3" customWidth="1"/>
+    <col min="19" max="16354" width="8.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="17.649999999999999" customHeight="1">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="17.649999999999999" customHeight="1">
       <c r="A1" s="8"/>
       <c r="C1" s="6"/>
       <c r="E1" s="6"/>
@@ -1691,75 +1695,76 @@
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
-    </row>
-    <row r="2" spans="1:17" ht="17.649999999999999" customHeight="1">
+      <c r="R1" s="6"/>
+    </row>
+    <row r="2" spans="1:18" ht="17.649999999999999" customHeight="1">
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" spans="1:17" ht="17.649999999999999" customHeight="1">
+    <row r="3" spans="1:18" ht="17.649999999999999" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" spans="1:17" ht="17.649999999999999" customHeight="1">
+    <row r="4" spans="1:18" ht="17.649999999999999" customHeight="1">
       <c r="A4" s="18" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:17" ht="17.649999999999999" customHeight="1">
+    <row r="5" spans="1:18" ht="17.649999999999999" customHeight="1">
       <c r="A5" s="18" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="4"/>
     </row>
-    <row r="6" spans="1:17" ht="17.649999999999999" customHeight="1">
+    <row r="6" spans="1:18" ht="17.649999999999999" customHeight="1">
       <c r="A6" s="18" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:17" ht="17.649999999999999" customHeight="1">
+    <row r="7" spans="1:18" ht="17.649999999999999" customHeight="1">
       <c r="A7" s="18" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="4"/>
     </row>
-    <row r="8" spans="1:17" ht="17.649999999999999" customHeight="1">
+    <row r="8" spans="1:18" ht="17.649999999999999" customHeight="1">
       <c r="A8" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:17" ht="17.649999999999999" customHeight="1">
+    <row r="9" spans="1:18" ht="17.649999999999999" customHeight="1">
       <c r="A9" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" spans="1:17" ht="17.649999999999999" customHeight="1">
+    <row r="10" spans="1:18" ht="17.649999999999999" customHeight="1">
       <c r="A10" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:17" ht="17.649999999999999" customHeight="1">
+    <row r="11" spans="1:18" ht="17.649999999999999" customHeight="1">
       <c r="A11" s="18" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:17" ht="17.649999999999999" customHeight="1">
+    <row r="12" spans="1:18" ht="17.649999999999999" customHeight="1">
       <c r="A12" s="18" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:17" s="2" customFormat="1" ht="17.649999999999999" customHeight="1">
+    <row r="13" spans="1:18" s="2" customFormat="1" ht="17.649999999999999" customHeight="1">
       <c r="A13" s="13" t="s">
         <v>2</v>
       </c>
@@ -1811,8 +1816,11 @@
       <c r="Q13" s="13" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" ht="17.649999999999999" customHeight="1">
+      <c r="R13" s="13" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="17.649999999999999" customHeight="1">
       <c r="A14" s="16"/>
       <c r="B14" s="15"/>
       <c r="C14" s="16"/>
@@ -1830,6 +1838,7 @@
       <c r="O14" s="16"/>
       <c r="P14" s="16"/>
       <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
